--- a/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catalogo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,11 +942,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -987,11 +987,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1031,11 +1031,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1111,11 +1111,11 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -1245,11 +1245,11 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2158,11 +2158,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -2254,11 +2254,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -2302,11 +2302,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -2350,11 +2350,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -3368,13 +3368,57 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Factor 4. Mejoramiento continuo y autorregulación</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Característica 14. Procesos de autorregulación</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continuar fortaleciendo los procesos de auditoría en el marco del modelo de control interno institucional, para monitorear el cumplimiento de políticas, procesos y procedimientos institucionales </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Efectividad de las acciones derivadas de las oportunidades de mejora</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>(Acciones cerradas calificadas como efectivas ÷ Total de acciones cerradas y evaluadas) × 100</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Director de control interno</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>%FRAC</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
@@ -489,7 +489,6 @@
           <t>Índice de Favorabilidad sobre la Misión Institucional.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Gerente de Planeación y Gestión / Aseguramiento de la calidad</t>
@@ -533,13 +532,11 @@
           <t>Índice de Favorabilidad sobre el PEI  Institucional</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Gerente de Planeación y Gestión / Aseguramiento de la calidad</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -573,7 +570,6 @@
           <t>Participación de estudiantes en Actividades de Formación Integral curricular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Investigación</t>
@@ -617,7 +613,6 @@
           <t>Participación de estudiantes en Actividades de Formación Integral  extracurricular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Centro de Psicologia</t>
@@ -720,7 +715,6 @@
           <t>Planeación Estratégica</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>ENT</t>
@@ -756,9 +750,6 @@
 Convenios</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -797,7 +788,6 @@
           <t>% de aumento de participación en jornada de rendición de cuentas Virtual- Presencial- Offline</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -841,7 +831,6 @@
           <t>Promedio de satisfacción de rendición de cuentas</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -929,7 +918,6 @@
 (Colaboradores, Graduados, Estudiantes)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Dirección de comunicaciones</t>
@@ -974,7 +962,6 @@
 (Colaboradores, Graduados, Estudiantes)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Dirección de comunicaciones</t>
@@ -1018,7 +1005,6 @@
           <t>Total Leads por canales de captación</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Gerencia de mercadeo</t>
@@ -1062,8 +1048,6 @@
           <t>Utilización de los estudiantes del CREA</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Semestral</t>
@@ -1102,13 +1086,11 @@
           <t>Satisfacción del proceso de comunicaciones</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Experiencia</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -1142,8 +1124,6 @@
           <t>Crecimiento de Ingresos de portafolio de Extensión</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -1193,7 +1173,6 @@
 Inversiones en bienestar</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -1242,7 +1221,6 @@
           <t>Gerencia de Planeación y Gestión institucional</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -1286,7 +1264,6 @@
           <t>Director de auditoria</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -1330,7 +1307,6 @@
           <t>Director de aseguramiento de la calidad/ Estudios Internos</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -1465,7 +1441,6 @@
           <t>Resultados evaluación 360°</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -1514,7 +1489,6 @@
           <t>Dirección de docencia</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>%</t>
@@ -1549,9 +1523,6 @@
 Modelo de gestión, evaluación e innovación curricular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -1643,7 +1614,6 @@
           <t>Dirección de Aseguramiento de la Calidad</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>ENT</t>
@@ -1677,13 +1647,11 @@
           <t>Número de programas nuevos con registro calificado aprobado</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Dirección de Aseguramiento de la Calidad</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>ENT</t>
@@ -1717,13 +1685,11 @@
           <t>N" programas con renovación de registro calificado</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Dirección de Aseguramiento de la Calidad</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -1805,13 +1771,11 @@
           <t>% de grupos de investigación  clasificados en A1, A y B</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Dirección de investigación, innovación y creación</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -1845,7 +1809,6 @@
           <t>Número de proyectos de investigación de Innovación y Creación con impacto</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Dirección de investigación, innovación y creación</t>
@@ -1889,13 +1852,11 @@
           <t>Número de productos de Nuevo conocimiento, desarrollo tecnológico, innovación y creación que impacten en la enseñanza y el aprendizaje por grupo de investigación</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Dirección de investigación, innovación y creación</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>ENT</t>
@@ -1929,7 +1890,6 @@
           <t>% de profesores TC clasificados como investigadores en Minciencias</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Dirección de investigación, innovación y creación</t>
@@ -1978,8 +1938,6 @@
           <t>(N° de estudiantes participantes en actividades de Extensión y proyección social/ Total de estudiantes)*100 Bogotá - Virtual</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -2018,8 +1976,6 @@
           <t>N° de estudiantes participantes en actividades de cultura y deporte</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -2053,8 +2009,6 @@
           <t xml:space="preserve">Participación ingresos por extensión (Consultorias, alquiler de espacios, prestación de servicios, centros de investigación entre otros) / total ingresos </t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -2387,8 +2341,6 @@
           <t>(Número de participantes en actividades de bienestar / Número total de miembros de la comunidad)*100</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2427,8 +2379,6 @@
           <t>Resultados instrumentos de satisfacción</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2473,7 +2423,6 @@
           <t>CX</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2518,7 +2467,6 @@
           <t>CX</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2557,8 +2505,6 @@
           <t>(N.º de actividades realizadas para modalidad virtual o regiones / N.º total de actividades de bienestar) × 100</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2602,7 +2548,6 @@
           <t>Dirección de docencia</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2647,7 +2592,6 @@
           <t>Dirección de docencia</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>%</t>
@@ -2691,7 +2635,6 @@
           <t>Dirección de docencia</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -2735,7 +2678,6 @@
           <t>Dirección de docencia</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2774,8 +2716,6 @@
           <t>(N° de profesores con escalafon docente/N° de cupos aprobados para el escalafon docente)*100</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2819,7 +2759,6 @@
           <t>Dirección de formación</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -2858,7 +2797,6 @@
           <t>N.º de docentes que participan en programas de fomento al multilingüismo/ Total de profesores tiempo completo y medio tiempo</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -2902,8 +2840,6 @@
           <t>N° de estudiantes impactados por las campañas de comunicación de reglamento estudiantil</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>DEC</t>
@@ -2947,7 +2883,6 @@
           <t>Dirección de experiencia</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>%FRAC</t>
@@ -3079,7 +3014,6 @@
 Modalidad y nivel</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Gerencia de servicio y permanencia</t>
@@ -3133,14 +3067,13 @@
           <t>Gerencia de servicio y permanencia</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -3172,7 +3105,6 @@
           <t>(Número de estudiantes con becas y apoyos financieros / Total de estudiantes ) × 100</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Validar</t>
@@ -3226,14 +3158,13 @@
           <t>Dirección de graduados</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -3265,7 +3196,6 @@
           <t>% de cotización del graduado</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Anual</t>
@@ -3317,14 +3247,13 @@
           <t>Dirección de graduados</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>%FRAC</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -3409,7 +3338,6 @@
           <t>Director de control interno</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>%FRAC</t>

--- a/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
@@ -1161,7 +1161,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Inversion al plan de mejoramiento</t>
+          <t>Inversión al plan de mejoramiento</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Valor agregado en la pruebas Saber Pro Institucional- Modelo PSM</t>
+          <t>Valor agregado en la pruebas Saber Pro Institucional</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Participación ingresos por extensión (Consultorias, alquiler de espacios, prestación de servicios, centros de investigación entre otros) / total ingresos </t>
+          <t>Participación ingresos por extensión (Consultorías, alquiler de espacios, prestación de servicios, centros de investigación entre otros) / total ingresos</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Indice de impacto Psicosocial de las actividades de bienestar</t>
+          <t>Índice de impacto Psicosocial de las actividades de bienestar</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Proporción de profesores con nivel de formación (Maestria y Doctorado)</t>
+          <t>Proporción de profesores con nivel de formación (Maestría y Doctorado)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>N° de cupos aprobados para el escalafon docente</t>
+          <t>N° de cupos aprobados para el escalafón docente</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tasa de empleabilidad de recièn graduados de pregrado</t>
+          <t>Tasa de empleabilidad de recién graduados de pregrado</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Nivel de Satisfacción del graduado con la institución (Experiencia)</t>
+          <t>Nivel de Satisfacción del graduado con la institución</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">

--- a/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
+++ b/data/raw/Plan de mejoramiento/Catalogo_Indicadores_Plan_Mejoramiento.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Catalogo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>N" programas con renovación de registro calificado</t>
+          <t>Número de programas con renovación de registro calificado</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
